--- a/data/trans_orig/P5708-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P5708-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de tener la posibilidad de hablar con alguien de mis problemas económicos en 2007</t>
+          <t>Población según la frecuencia de tener la posibilidad de hablar con alguien de mis problemas económicos en 2007 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>298565</t>
+          <t>297025</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>350518</t>
+          <t>349270</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>43,02%</t>
+          <t>42,8%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>50,51%</t>
+          <t>50,33%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>274349</t>
+          <t>268762</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>323732</t>
+          <t>323048</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>39,86%</t>
+          <t>39,04%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>47,03%</t>
+          <t>46,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>586119</t>
+          <t>587672</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>658092</t>
+          <t>658436</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>42,4%</t>
+          <t>42,51%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>47,61%</t>
+          <t>47,63%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>197317</t>
+          <t>198238</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>245092</t>
+          <t>248347</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>28,43%</t>
+          <t>28,56%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>35,32%</t>
+          <t>35,78%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>189475</t>
+          <t>192273</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>236004</t>
+          <t>240465</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>27,53%</t>
+          <t>27,93%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>34,29%</t>
+          <t>34,93%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>402889</t>
+          <t>405841</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>469783</t>
+          <t>472240</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>29,36%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>33,98%</t>
+          <t>34,16%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>108838</t>
+          <t>107072</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>146645</t>
+          <t>147737</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>116299</t>
+          <t>115272</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>156500</t>
+          <t>159441</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>23,16%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>237498</t>
+          <t>237619</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>292624</t>
+          <t>291995</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>21,12%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12076</t>
+          <t>11625</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30807</t>
+          <t>29693</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>26569</t>
+          <t>25708</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>49109</t>
+          <t>49298</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>42036</t>
+          <t>41539</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>72122</t>
+          <t>72231</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,23%</t>
         </is>
       </c>
     </row>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4381</t>
+          <t>4852</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1205,7 +1205,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1225,7 +1225,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>8370</t>
+          <t>8412</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1002</t>
+          <t>999</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>10336</t>
+          <t>9683</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,7%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>508687</t>
+          <t>509983</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>571531</t>
+          <t>573140</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>52,89%</t>
+          <t>53,02%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>59,42%</t>
+          <t>59,59%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>509323</t>
+          <t>508417</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>572909</t>
+          <t>571623</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>52,59%</t>
+          <t>52,5%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>59,16%</t>
+          <t>59,03%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1035270</t>
+          <t>1033376</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1121228</t>
+          <t>1118277</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>53,64%</t>
+          <t>53,54%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>58,09%</t>
+          <t>57,94%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>229630</t>
+          <t>227867</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>283002</t>
+          <t>284696</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>23,69%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>29,42%</t>
+          <t>29,6%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>233201</t>
+          <t>232486</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>291550</t>
+          <t>287694</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>24,01%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>30,11%</t>
+          <t>29,71%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>482255</t>
+          <t>481507</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>555257</t>
+          <t>559557</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>24,95%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>28,99%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>117383</t>
+          <t>116545</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>163264</t>
+          <t>161742</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>122023</t>
+          <t>126594</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>168884</t>
+          <t>173294</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>17,89%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>257331</t>
+          <t>252818</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>321037</t>
+          <t>315391</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>16,34%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14046</t>
+          <t>13694</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>32819</t>
+          <t>33621</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11433</t>
+          <t>11997</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>30217</t>
+          <t>31068</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>30785</t>
+          <t>30419</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>58379</t>
+          <t>57005</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,95%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1922</t>
+          <t>1965</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>10237</t>
+          <t>11789</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>974</t>
+          <t>968</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>8701</t>
+          <t>8070</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3880</t>
+          <t>3377</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>14163</t>
+          <t>15718</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,81%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>381893</t>
+          <t>379096</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>434250</t>
+          <t>430900</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>56,28%</t>
+          <t>55,87%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>64,0%</t>
+          <t>63,51%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>389885</t>
+          <t>396253</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>442983</t>
+          <t>446076</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>57,01%</t>
+          <t>57,95%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>64,78%</t>
+          <t>65,23%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>786390</t>
+          <t>790546</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>861782</t>
+          <t>863080</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>57,72%</t>
+          <t>58,03%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>63,26%</t>
+          <t>63,35%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>145705</t>
+          <t>147231</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>192058</t>
+          <t>194677</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>28,31%</t>
+          <t>28,69%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>127216</t>
+          <t>127126</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>168128</t>
+          <t>168785</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>24,68%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>286089</t>
+          <t>284870</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>352361</t>
+          <t>346023</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>20,91%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>25,4%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>63872</t>
+          <t>63959</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>99654</t>
+          <t>99890</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>74056</t>
+          <t>73120</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>108197</t>
+          <t>107195</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>145009</t>
+          <t>147978</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>194446</t>
+          <t>195547</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,35%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11074</t>
+          <t>11470</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>28920</t>
+          <t>30438</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>16609</t>
+          <t>16942</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>37500</t>
+          <t>39181</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>33351</t>
+          <t>32612</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>60513</t>
+          <t>59738</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,38%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>910</t>
+          <t>920</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>10609</t>
+          <t>9854</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2564,47 +2564,47 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
+          <t>0,14%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>1,45%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>3057</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>922</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>8471</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>0,45%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
           <t>0,13%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>1,56%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>3057</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>7975</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>0,45%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2111</t>
+          <t>2144</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>14282</t>
+          <t>13483</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>0,99%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>492384</t>
+          <t>493957</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>550393</t>
+          <t>555636</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>52,34%</t>
+          <t>52,51%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>58,51%</t>
+          <t>59,07%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>550522</t>
+          <t>548304</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>614227</t>
+          <t>612103</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>53,06%</t>
+          <t>52,84%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>59,2%</t>
+          <t>58,99%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1061937</t>
+          <t>1063402</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1149883</t>
+          <t>1145666</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>53,68%</t>
+          <t>53,75%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>58,12%</t>
+          <t>57,91%</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>235920</t>
+          <t>235207</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>291465</t>
+          <t>290258</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2907,12 +2907,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>25,08%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>30,98%</t>
+          <t>30,86%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>212043</t>
+          <t>212753</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>267515</t>
+          <t>267050</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>25,78%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>459303</t>
+          <t>462954</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>537170</t>
+          <t>537403</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>23,4%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>27,15%</t>
+          <t>27,16%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>94522</t>
+          <t>94872</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>132788</t>
+          <t>134645</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>131972</t>
+          <t>130577</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>176091</t>
+          <t>174775</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>236506</t>
+          <t>235177</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>295873</t>
+          <t>297619</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>15,04%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>30009</t>
+          <t>29297</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>56347</t>
+          <t>55695</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>42999</t>
+          <t>42775</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>72629</t>
+          <t>71686</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>78781</t>
+          <t>78627</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>119401</t>
+          <t>118095</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>5,97%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>840</t>
+          <t>876</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>7608</t>
+          <t>8400</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>4100</t>
+          <t>4439</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>15965</t>
+          <t>17064</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6648</t>
+          <t>6556</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>20783</t>
+          <t>20688</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,7 +3316,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3461,12 +3461,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1732177</t>
+          <t>1734981</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1847536</t>
+          <t>1851462</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3476,12 +3476,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>52,89%</t>
+          <t>52,98%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>56,41%</t>
+          <t>56,53%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1783870</t>
+          <t>1781930</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1895887</t>
+          <t>1896253</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>52,81%</t>
+          <t>52,75%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>56,12%</t>
+          <t>56,13%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3555654</t>
+          <t>3547712</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3723075</t>
+          <t>3710601</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>53,44%</t>
+          <t>53,32%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>55,96%</t>
+          <t>55,77%</t>
         </is>
       </c>
     </row>
@@ -3574,12 +3574,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>857587</t>
+          <t>858890</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>959097</t>
+          <t>962178</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3589,12 +3589,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>26,19%</t>
+          <t>26,23%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>29,38%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3609,12 +3609,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>807475</t>
+          <t>805817</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>906453</t>
+          <t>913691</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>23,85%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>27,05%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3644,12 +3644,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1690214</t>
+          <t>1691308</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1831073</t>
+          <t>1837214</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>25,42%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>27,52%</t>
+          <t>27,61%</t>
         </is>
       </c>
     </row>
@@ -3687,12 +3687,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>417947</t>
+          <t>420871</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>499413</t>
+          <t>500447</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3702,12 +3702,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3722,12 +3722,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>485360</t>
+          <t>483733</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>570200</t>
+          <t>569322</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3737,12 +3737,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3757,12 +3757,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>925775</t>
+          <t>928719</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1041884</t>
+          <t>1043851</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3772,12 +3772,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>15,69%</t>
         </is>
       </c>
     </row>
@@ -3800,12 +3800,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>81988</t>
+          <t>82329</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>122402</t>
+          <t>122619</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3815,7 +3815,7 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>117016</t>
+          <t>116761</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>164739</t>
+          <t>163781</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3855,7 +3855,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>208112</t>
+          <t>211282</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>272012</t>
+          <t>272309</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3885,7 +3885,7 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -3913,12 +3913,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>7282</t>
+          <t>7325</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>21308</t>
+          <t>20926</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3933,7 +3933,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>10413</t>
+          <t>10581</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>27580</t>
+          <t>29180</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3968,7 +3968,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3983,12 +3983,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>20478</t>
+          <t>21145</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>43463</t>
+          <t>42690</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3998,12 +3998,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,64%</t>
         </is>
       </c>
     </row>
@@ -4180,7 +4180,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de tener la posibilidad de hablar con alguien de mis problemas económicos en 2012</t>
+          <t>Población según la frecuencia de tener la posibilidad de hablar con alguien de mis problemas económicos en 2012 (tasa de respuesta: 99,63%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4375,12 +4375,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>424620</t>
+          <t>425714</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>476773</t>
+          <t>477532</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4390,12 +4390,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>60,7%</t>
+          <t>60,85%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>68,15%</t>
+          <t>68,26%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>391353</t>
+          <t>389589</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>444790</t>
+          <t>443005</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4425,12 +4425,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>56,14%</t>
+          <t>55,89%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>63,81%</t>
+          <t>63,55%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>831927</t>
+          <t>832809</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>904326</t>
+          <t>906465</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4460,12 +4460,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>59,57%</t>
+          <t>59,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>64,75%</t>
+          <t>64,9%</t>
         </is>
       </c>
     </row>
@@ -4488,12 +4488,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>152653</t>
+          <t>153979</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>198666</t>
+          <t>200610</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4503,12 +4503,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>22,01%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>28,68%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4523,12 +4523,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>177892</t>
+          <t>178876</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>228531</t>
+          <t>226403</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4538,12 +4538,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>25,52%</t>
+          <t>25,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>32,79%</t>
+          <t>32,48%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4558,12 +4558,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>346387</t>
+          <t>343824</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>414989</t>
+          <t>411028</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4573,12 +4573,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>24,62%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>29,71%</t>
+          <t>29,43%</t>
         </is>
       </c>
     </row>
@@ -4601,12 +4601,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>39184</t>
+          <t>39545</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>67704</t>
+          <t>67565</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4616,12 +4616,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4636,12 +4636,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>37815</t>
+          <t>38666</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>68011</t>
+          <t>67210</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4671,12 +4671,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>84391</t>
+          <t>84629</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>125060</t>
+          <t>124044</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4686,12 +4686,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>8,88%</t>
         </is>
       </c>
     </row>
@@ -4714,12 +4714,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7864</t>
+          <t>7433</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22524</t>
+          <t>21718</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4729,12 +4729,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4749,12 +4749,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12579</t>
+          <t>12615</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>31465</t>
+          <t>31979</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4764,12 +4764,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4784,12 +4784,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>22591</t>
+          <t>23838</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>46857</t>
+          <t>48398</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4799,12 +4799,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,47%</t>
         </is>
       </c>
     </row>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2045</t>
+          <t>1904</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>12611</t>
+          <t>12099</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4842,12 +4842,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4862,12 +4862,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1977</t>
+          <t>1918</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>11223</t>
+          <t>11366</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4882,7 +4882,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4897,12 +4897,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>5604</t>
+          <t>5713</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>18613</t>
+          <t>18362</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4912,12 +4912,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,31%</t>
         </is>
       </c>
     </row>
@@ -5057,12 +5057,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>579077</t>
+          <t>577625</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>641350</t>
+          <t>643401</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5072,12 +5072,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>57,31%</t>
+          <t>57,17%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>63,47%</t>
+          <t>63,67%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5092,12 +5092,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>538598</t>
+          <t>539270</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>602809</t>
+          <t>605800</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5107,12 +5107,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>52,29%</t>
+          <t>52,35%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>58,52%</t>
+          <t>58,81%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5127,12 +5127,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1135786</t>
+          <t>1131438</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1228368</t>
+          <t>1223680</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5142,12 +5142,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>55,66%</t>
+          <t>55,45%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>60,2%</t>
+          <t>59,97%</t>
         </is>
       </c>
     </row>
@@ -5170,12 +5170,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>229206</t>
+          <t>227627</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>285163</t>
+          <t>284870</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5185,12 +5185,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>28,19%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5205,12 +5205,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>300537</t>
+          <t>300197</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>364724</t>
+          <t>363938</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5220,12 +5220,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>29,17%</t>
+          <t>29,14%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>35,41%</t>
+          <t>35,33%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5240,12 +5240,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>541196</t>
+          <t>548603</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>627366</t>
+          <t>629451</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5255,12 +5255,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>26,88%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>30,74%</t>
+          <t>30,85%</t>
         </is>
       </c>
     </row>
@@ -5283,12 +5283,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>87059</t>
+          <t>88377</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>127116</t>
+          <t>128029</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5298,12 +5298,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5318,12 +5318,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>85775</t>
+          <t>84817</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>125473</t>
+          <t>124756</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5353,12 +5353,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>182109</t>
+          <t>181302</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>238904</t>
+          <t>239201</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,72%</t>
         </is>
       </c>
     </row>
@@ -5396,12 +5396,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>22741</t>
+          <t>23206</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>48275</t>
+          <t>48079</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5411,12 +5411,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5431,12 +5431,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10934</t>
+          <t>10285</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>29488</t>
+          <t>28712</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5446,12 +5446,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5466,12 +5466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>38186</t>
+          <t>39299</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>69637</t>
+          <t>70269</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5481,12 +5481,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,44%</t>
         </is>
       </c>
     </row>
@@ -5509,12 +5509,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1050</t>
+          <t>1132</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>10772</t>
+          <t>10506</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5524,12 +5524,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5544,12 +5544,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1864</t>
+          <t>1861</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>14313</t>
+          <t>14807</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5564,7 +5564,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5579,12 +5579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4161</t>
+          <t>4220</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>20489</t>
+          <t>20623</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5594,12 +5594,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,01%</t>
         </is>
       </c>
     </row>
@@ -5739,12 +5739,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>417963</t>
+          <t>424400</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>480477</t>
+          <t>479144</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5754,12 +5754,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>55,49%</t>
+          <t>56,35%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>63,79%</t>
+          <t>63,61%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5774,12 +5774,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>424514</t>
+          <t>427536</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>486086</t>
+          <t>483503</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>54,62%</t>
+          <t>55,01%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>62,55%</t>
+          <t>62,21%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5809,12 +5809,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>868691</t>
+          <t>863406</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>947712</t>
+          <t>946343</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>56,76%</t>
+          <t>56,42%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>61,93%</t>
+          <t>61,84%</t>
         </is>
       </c>
     </row>
@@ -5852,12 +5852,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>164337</t>
+          <t>166566</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>218016</t>
+          <t>212504</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5867,12 +5867,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>22,11%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>28,21%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5887,12 +5887,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>185117</t>
+          <t>182352</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>238994</t>
+          <t>236169</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5902,12 +5902,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>23,46%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>30,75%</t>
+          <t>30,39%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5922,12 +5922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>363052</t>
+          <t>364267</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>434661</t>
+          <t>436632</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5937,12 +5937,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>28,53%</t>
         </is>
       </c>
     </row>
@@ -5965,12 +5965,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>71239</t>
+          <t>69714</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>111698</t>
+          <t>111227</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5980,12 +5980,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6000,12 +6000,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>67177</t>
+          <t>67250</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>104778</t>
+          <t>103483</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6015,12 +6015,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6035,12 +6035,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>150290</t>
+          <t>149339</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>202028</t>
+          <t>202496</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,23%</t>
         </is>
       </c>
     </row>
@@ -6078,12 +6078,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7060</t>
+          <t>7095</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>22298</t>
+          <t>21769</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6098,7 +6098,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>11282</t>
+          <t>11752</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>30155</t>
+          <t>30812</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>21784</t>
+          <t>22666</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>46630</t>
+          <t>45438</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>2,97%</t>
         </is>
       </c>
     </row>
@@ -6191,12 +6191,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3611</t>
+          <t>3861</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>17917</t>
+          <t>18433</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6206,12 +6206,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3944</t>
+          <t>4011</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>15270</t>
+          <t>16123</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>9448</t>
+          <t>9756</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>27542</t>
+          <t>28376</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,85%</t>
         </is>
       </c>
     </row>
@@ -6421,12 +6421,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>502921</t>
+          <t>502726</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>564085</t>
+          <t>563860</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6436,12 +6436,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>53,25%</t>
+          <t>53,23%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>59,72%</t>
+          <t>59,7%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>529469</t>
+          <t>527841</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>593795</t>
+          <t>593341</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>50,53%</t>
+          <t>50,38%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>56,67%</t>
+          <t>56,63%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1047714</t>
+          <t>1043259</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1143459</t>
+          <t>1142569</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>52,59%</t>
+          <t>52,36%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>57,39%</t>
+          <t>57,35%</t>
         </is>
       </c>
     </row>
@@ -6534,12 +6534,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>241661</t>
+          <t>243849</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>297691</t>
+          <t>301726</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6549,12 +6549,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>25,59%</t>
+          <t>25,82%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>31,52%</t>
+          <t>31,94%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6569,12 +6569,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>300473</t>
+          <t>302076</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>361488</t>
+          <t>365586</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6584,12 +6584,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>28,68%</t>
+          <t>28,83%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>34,89%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>557496</t>
+          <t>559810</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>646316</t>
+          <t>644836</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6619,12 +6619,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>28,1%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>32,44%</t>
+          <t>32,37%</t>
         </is>
       </c>
     </row>
@@ -6647,12 +6647,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>93910</t>
+          <t>92931</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>135924</t>
+          <t>134725</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6662,12 +6662,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6682,12 +6682,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>101954</t>
+          <t>101676</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>146564</t>
+          <t>145095</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6697,12 +6697,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6717,12 +6717,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>206603</t>
+          <t>204159</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>264649</t>
+          <t>263890</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6732,12 +6732,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>13,25%</t>
         </is>
       </c>
     </row>
@@ -6760,12 +6760,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>13547</t>
+          <t>13703</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>32995</t>
+          <t>32035</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6775,12 +6775,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6795,12 +6795,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>11469</t>
+          <t>11798</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>29610</t>
+          <t>29807</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6810,12 +6810,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6830,12 +6830,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>28671</t>
+          <t>29375</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>54548</t>
+          <t>55194</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6845,12 +6845,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,77%</t>
         </is>
       </c>
     </row>
@@ -6873,12 +6873,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2336</t>
+          <t>1983</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>13808</t>
+          <t>12948</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6888,12 +6888,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6908,12 +6908,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>8182</t>
+          <t>8139</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>25420</t>
+          <t>26003</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6928,7 +6928,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6943,12 +6943,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>13095</t>
+          <t>12539</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>32969</t>
+          <t>31368</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6958,12 +6958,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,57%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1992669</t>
+          <t>1991753</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2109274</t>
+          <t>2104322</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>58,47%</t>
+          <t>58,45%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>61,9%</t>
+          <t>61,75%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1946615</t>
+          <t>1942758</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2068301</t>
+          <t>2064292</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7153,12 +7153,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>54,8%</t>
+          <t>54,69%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>58,23%</t>
+          <t>58,11%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3972614</t>
+          <t>3969442</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4147922</t>
+          <t>4144682</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>57,08%</t>
+          <t>57,03%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>59,6%</t>
+          <t>59,55%</t>
         </is>
       </c>
     </row>
@@ -7216,12 +7216,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>844438</t>
+          <t>839091</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>946486</t>
+          <t>941095</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7231,12 +7231,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>24,62%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>27,77%</t>
+          <t>27,62%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7251,12 +7251,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1018334</t>
+          <t>1017254</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1130909</t>
+          <t>1130641</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7266,12 +7266,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>28,64%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>31,84%</t>
+          <t>31,83%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1875716</t>
+          <t>1878093</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2037877</t>
+          <t>2044452</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7301,12 +7301,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>26,98%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>29,37%</t>
         </is>
       </c>
     </row>
@@ -7329,12 +7329,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>325645</t>
+          <t>326038</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>400544</t>
+          <t>401073</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7344,12 +7344,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7364,12 +7364,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>324606</t>
+          <t>326027</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>401277</t>
+          <t>399961</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7379,12 +7379,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7399,12 +7399,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>672930</t>
+          <t>668817</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>779425</t>
+          <t>776996</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,16%</t>
         </is>
       </c>
     </row>
@@ -7442,12 +7442,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>65754</t>
+          <t>63876</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>102445</t>
+          <t>100733</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7457,82 +7457,82 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
+          <t>1,87%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>2,96%</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>77150</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>60878</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>95959</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>2,17%</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>1,71%</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>2,7%</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr">
+        <is>
+          <t>158960</t>
+        </is>
+      </c>
+      <c r="S31" s="2" t="inlineStr">
+        <is>
+          <t>134536</t>
+        </is>
+      </c>
+      <c r="T31" s="2" t="inlineStr">
+        <is>
+          <t>187632</t>
+        </is>
+      </c>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>2,28%</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
           <t>1,93%</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>3,01%</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>77150</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr">
-        <is>
-          <t>60308</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr">
-        <is>
-          <t>97550</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="inlineStr">
-        <is>
-          <t>2,17%</t>
-        </is>
-      </c>
-      <c r="O31" s="2" t="inlineStr">
-        <is>
-          <t>1,7%</t>
-        </is>
-      </c>
-      <c r="P31" s="2" t="inlineStr">
-        <is>
-          <t>2,75%</t>
-        </is>
-      </c>
-      <c r="Q31" s="2" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
-      <c r="R31" s="2" t="inlineStr">
-        <is>
-          <t>158960</t>
-        </is>
-      </c>
-      <c r="S31" s="2" t="inlineStr">
-        <is>
-          <t>133761</t>
-        </is>
-      </c>
-      <c r="T31" s="2" t="inlineStr">
-        <is>
-          <t>185837</t>
-        </is>
-      </c>
-      <c r="U31" s="2" t="inlineStr">
-        <is>
-          <t>2,28%</t>
-        </is>
-      </c>
-      <c r="V31" s="2" t="inlineStr">
-        <is>
-          <t>1,92%</t>
-        </is>
-      </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,7%</t>
         </is>
       </c>
     </row>
@@ -7555,12 +7555,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>15771</t>
+          <t>16035</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>36568</t>
+          <t>38674</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7570,12 +7570,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7590,12 +7590,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>23604</t>
+          <t>23539</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>48739</t>
+          <t>48216</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7610,7 +7610,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7625,12 +7625,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>44237</t>
+          <t>44099</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>75978</t>
+          <t>77962</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7640,12 +7640,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,12%</t>
         </is>
       </c>
     </row>
@@ -7822,7 +7822,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de tener la posibilidad de hablar con alguien de mis problemas económicos en 2016</t>
+          <t>Población según la frecuencia de tener la posibilidad de hablar con alguien de mis problemas económicos en 2016 (tasa de respuesta: 99,68%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8017,12 +8017,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>310409</t>
+          <t>311697</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>363591</t>
+          <t>363700</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8032,12 +8032,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>46,15%</t>
+          <t>46,34%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>54,05%</t>
+          <t>54,07%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>292249</t>
+          <t>297530</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>345490</t>
+          <t>347402</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8067,12 +8067,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>43,56%</t>
+          <t>44,35%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>51,5%</t>
+          <t>51,78%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8087,12 +8087,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>623402</t>
+          <t>617275</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>696202</t>
+          <t>691551</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8102,12 +8102,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>46,4%</t>
+          <t>45,94%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>51,82%</t>
+          <t>51,47%</t>
         </is>
       </c>
     </row>
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>197317</t>
+          <t>195944</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>246127</t>
+          <t>244662</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8145,12 +8145,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>29,33%</t>
+          <t>29,13%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>36,59%</t>
+          <t>36,37%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8165,12 +8165,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>203650</t>
+          <t>203051</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>253764</t>
+          <t>251061</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8180,12 +8180,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>30,36%</t>
+          <t>30,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>37,83%</t>
+          <t>37,42%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8200,12 +8200,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>415365</t>
+          <t>416838</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>484271</t>
+          <t>485274</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8215,12 +8215,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>30,92%</t>
+          <t>31,03%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>36,05%</t>
+          <t>36,12%</t>
         </is>
       </c>
     </row>
@@ -8243,12 +8243,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>71784</t>
+          <t>72116</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>107270</t>
+          <t>106935</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8258,12 +8258,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8278,12 +8278,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>81900</t>
+          <t>82044</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>117807</t>
+          <t>116056</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8293,12 +8293,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8313,12 +8313,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>159750</t>
+          <t>161906</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>213781</t>
+          <t>214442</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8328,12 +8328,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>15,96%</t>
         </is>
       </c>
     </row>
@@ -8356,12 +8356,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14790</t>
+          <t>14185</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>36581</t>
+          <t>35085</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8371,12 +8371,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8391,12 +8391,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10034</t>
+          <t>9235</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>27669</t>
+          <t>27635</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8406,7 +8406,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -8426,12 +8426,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>29031</t>
+          <t>27838</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>54597</t>
+          <t>53322</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>3,97%</t>
         </is>
       </c>
     </row>
@@ -8469,12 +8469,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>989</t>
+          <t>998</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8102</t>
+          <t>8989</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8489,7 +8489,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8504,12 +8504,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2063</t>
+          <t>2175</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>13323</t>
+          <t>13212</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8519,12 +8519,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8539,12 +8539,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4093</t>
+          <t>4248</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>16392</t>
+          <t>17129</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,27%</t>
         </is>
       </c>
     </row>
@@ -8699,12 +8699,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>524482</t>
+          <t>522492</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>586888</t>
+          <t>588633</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8714,12 +8714,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>51,5%</t>
+          <t>51,31%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>57,63%</t>
+          <t>57,8%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8734,12 +8734,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>526611</t>
+          <t>527353</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>591348</t>
+          <t>592767</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8749,12 +8749,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>50,54%</t>
+          <t>50,61%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>56,76%</t>
+          <t>56,89%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8769,12 +8769,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1065250</t>
+          <t>1064085</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1160035</t>
+          <t>1158811</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>51,7%</t>
+          <t>51,65%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>56,31%</t>
+          <t>56,25%</t>
         </is>
       </c>
     </row>
@@ -8812,12 +8812,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>278751</t>
+          <t>277009</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>338279</t>
+          <t>337434</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8827,12 +8827,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>27,37%</t>
+          <t>27,2%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>33,22%</t>
+          <t>33,14%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8847,12 +8847,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>296618</t>
+          <t>292694</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>354327</t>
+          <t>356415</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8862,12 +8862,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>28,47%</t>
+          <t>28,09%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>34,01%</t>
+          <t>34,21%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8882,12 +8882,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>594098</t>
+          <t>594008</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>675507</t>
+          <t>678687</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>28,83%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>32,79%</t>
+          <t>32,94%</t>
         </is>
       </c>
     </row>
@@ -8925,12 +8925,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>111502</t>
+          <t>112862</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>154429</t>
+          <t>156071</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8940,12 +8940,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8960,12 +8960,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>113300</t>
+          <t>114403</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>160557</t>
+          <t>159074</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8975,12 +8975,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>236220</t>
+          <t>238063</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>303087</t>
+          <t>304057</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9010,12 +9010,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,76%</t>
         </is>
       </c>
     </row>
@@ -9038,12 +9038,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9269</t>
+          <t>9041</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25747</t>
+          <t>26211</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9073,12 +9073,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7433</t>
+          <t>7352</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>24322</t>
+          <t>24835</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9093,7 +9093,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9108,12 +9108,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>19673</t>
+          <t>19381</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>43624</t>
+          <t>43879</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9123,12 +9123,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,13%</t>
         </is>
       </c>
     </row>
@@ -9151,12 +9151,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1820</t>
+          <t>1814</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>11532</t>
+          <t>11174</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9171,7 +9171,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9186,12 +9186,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3004</t>
+          <t>2994</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>15032</t>
+          <t>15429</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9206,7 +9206,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5908</t>
+          <t>6070</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>20877</t>
+          <t>21034</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9241,7 +9241,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,02%</t>
         </is>
       </c>
     </row>
@@ -9381,12 +9381,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>289017</t>
+          <t>284998</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>342528</t>
+          <t>340903</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9396,12 +9396,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>38,23%</t>
+          <t>37,7%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>45,31%</t>
+          <t>45,1%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9416,12 +9416,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>280845</t>
+          <t>280263</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>337815</t>
+          <t>337614</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>36,15%</t>
+          <t>36,07%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>43,48%</t>
+          <t>43,46%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9451,12 +9451,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>582711</t>
+          <t>586986</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>663654</t>
+          <t>666108</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9466,12 +9466,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>38,02%</t>
+          <t>38,29%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>43,3%</t>
+          <t>43,46%</t>
         </is>
       </c>
     </row>
@@ -9494,12 +9494,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>235375</t>
+          <t>238052</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>288722</t>
+          <t>287836</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9509,12 +9509,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>31,14%</t>
+          <t>31,49%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>38,2%</t>
+          <t>38,08%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9529,12 +9529,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>262094</t>
+          <t>263070</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>319817</t>
+          <t>319546</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>33,73%</t>
+          <t>33,86%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>41,16%</t>
+          <t>41,13%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9564,12 +9564,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>516034</t>
+          <t>515026</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>594203</t>
+          <t>589397</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9579,12 +9579,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>33,67%</t>
+          <t>33,6%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>38,77%</t>
+          <t>38,45%</t>
         </is>
       </c>
     </row>
@@ -9607,12 +9607,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>143431</t>
+          <t>142657</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>189957</t>
+          <t>188993</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9622,12 +9622,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>18,87%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9642,12 +9642,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>136378</t>
+          <t>134588</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>184787</t>
+          <t>183416</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9657,12 +9657,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>23,61%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>292616</t>
+          <t>293620</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>358816</t>
+          <t>362560</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9692,12 +9692,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>23,41%</t>
+          <t>23,65%</t>
         </is>
       </c>
     </row>
@@ -9720,12 +9720,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5016</t>
+          <t>4557</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>17733</t>
+          <t>18523</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9735,12 +9735,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>9538</t>
+          <t>9753</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>27656</t>
+          <t>27273</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9770,12 +9770,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9790,12 +9790,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>17335</t>
+          <t>17073</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>38927</t>
+          <t>39679</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9805,12 +9805,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,59%</t>
         </is>
       </c>
     </row>
@@ -9838,7 +9838,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>8222</t>
+          <t>8652</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9853,7 +9853,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9873,7 +9873,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>6950</t>
+          <t>6840</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9888,7 +9888,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9903,12 +9903,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1076</t>
+          <t>1440</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>10871</t>
+          <t>11827</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9918,12 +9918,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,77%</t>
         </is>
       </c>
     </row>
@@ -10063,12 +10063,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>465883</t>
+          <t>464668</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>524925</t>
+          <t>525377</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10078,12 +10078,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>49,81%</t>
+          <t>49,68%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>56,12%</t>
+          <t>56,17%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>531965</t>
+          <t>535797</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>599846</t>
+          <t>603155</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10113,12 +10113,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>51,05%</t>
+          <t>51,41%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>57,56%</t>
+          <t>57,88%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10133,12 +10133,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1017964</t>
+          <t>1017887</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1105809</t>
+          <t>1103306</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10153,7 +10153,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>55,92%</t>
+          <t>55,8%</t>
         </is>
       </c>
     </row>
@@ -10176,12 +10176,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>259232</t>
+          <t>259455</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>315757</t>
+          <t>314792</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10191,12 +10191,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>27,72%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>33,76%</t>
+          <t>33,66%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>271298</t>
+          <t>271373</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>331992</t>
+          <t>331888</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10226,12 +10226,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>26,04%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>31,86%</t>
+          <t>31,85%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10246,12 +10246,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>549135</t>
+          <t>550297</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>631038</t>
+          <t>629499</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10261,12 +10261,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>27,77%</t>
+          <t>27,83%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>31,91%</t>
+          <t>31,83%</t>
         </is>
       </c>
     </row>
@@ -10289,12 +10289,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>109004</t>
+          <t>109272</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>149995</t>
+          <t>149500</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10304,12 +10304,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10324,12 +10324,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>108887</t>
+          <t>107733</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>156295</t>
+          <t>154752</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10339,12 +10339,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10359,12 +10359,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>224498</t>
+          <t>226191</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>288148</t>
+          <t>288529</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10374,12 +10374,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,59%</t>
         </is>
       </c>
     </row>
@@ -10402,12 +10402,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>9623</t>
+          <t>9045</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>25953</t>
+          <t>25947</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10417,7 +10417,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -10437,12 +10437,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>26483</t>
+          <t>25813</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>50843</t>
+          <t>49288</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10452,12 +10452,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10472,12 +10472,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>39191</t>
+          <t>40499</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>70065</t>
+          <t>70404</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10487,12 +10487,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,56%</t>
         </is>
       </c>
     </row>
@@ -10515,12 +10515,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>4124</t>
+          <t>3483</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>16077</t>
+          <t>15797</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10530,12 +10530,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10550,12 +10550,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3209</t>
+          <t>2687</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>15203</t>
+          <t>14947</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10565,12 +10565,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10585,12 +10585,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>9348</t>
+          <t>9090</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>26960</t>
+          <t>26386</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10600,12 +10600,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,33%</t>
         </is>
       </c>
     </row>
@@ -10745,12 +10745,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1644272</t>
+          <t>1647619</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1764919</t>
+          <t>1763715</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10760,12 +10760,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>48,62%</t>
+          <t>48,71%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>52,18%</t>
+          <t>52,15%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10780,12 +10780,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1691283</t>
+          <t>1693232</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1815533</t>
+          <t>1817535</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10795,12 +10795,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>47,89%</t>
+          <t>47,94%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>51,41%</t>
+          <t>51,46%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10815,12 +10815,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3381452</t>
+          <t>3373147</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3556734</t>
+          <t>3544588</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>48,91%</t>
+          <t>48,79%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>51,44%</t>
+          <t>51,27%</t>
         </is>
       </c>
     </row>
@@ -10858,12 +10858,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1023287</t>
+          <t>1021559</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1138158</t>
+          <t>1127751</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10873,12 +10873,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>30,2%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>33,65%</t>
+          <t>33,34%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10893,12 +10893,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1093451</t>
+          <t>1088881</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1202688</t>
+          <t>1205985</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10908,12 +10908,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>30,96%</t>
+          <t>30,83%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>34,05%</t>
+          <t>34,15%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10928,12 +10928,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2148716</t>
+          <t>2150129</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2301310</t>
+          <t>2307743</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10943,12 +10943,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>31,1%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>33,28%</t>
+          <t>33,38%</t>
         </is>
       </c>
     </row>
@@ -10971,12 +10971,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>471654</t>
+          <t>471769</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>561556</t>
+          <t>562355</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10991,7 +10991,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11006,12 +11006,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>483484</t>
+          <t>481154</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>566897</t>
+          <t>570597</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11021,12 +11021,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11041,12 +11041,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>980945</t>
+          <t>986255</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1098430</t>
+          <t>1109204</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11056,12 +11056,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>16,04%</t>
         </is>
       </c>
     </row>
@@ -11084,12 +11084,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>49300</t>
+          <t>50315</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>82596</t>
+          <t>83969</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11099,12 +11099,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11119,12 +11119,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>66716</t>
+          <t>64402</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>104381</t>
+          <t>100609</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11134,12 +11134,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11154,12 +11154,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>123537</t>
+          <t>125514</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>176602</t>
+          <t>177678</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11169,12 +11169,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,57%</t>
         </is>
       </c>
     </row>
@@ -11197,12 +11197,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>11286</t>
+          <t>11624</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>29467</t>
+          <t>30683</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11212,12 +11212,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11232,12 +11232,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>13336</t>
+          <t>14152</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>33958</t>
+          <t>33679</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11247,12 +11247,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11267,12 +11267,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>29113</t>
+          <t>29761</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>56370</t>
+          <t>56874</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11282,7 +11282,7 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -11464,7 +11464,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de tener la posibilidad de hablar con alguien de mis problemas económicos en 2023</t>
+          <t>Población según la frecuencia de tener la posibilidad de hablar con alguien de mis problemas económicos en 2023 (tasa de respuesta: 99,37%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -11659,12 +11659,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>380416</t>
+          <t>380486</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>430925</t>
+          <t>430932</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -11674,7 +11674,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>60,14%</t>
+          <t>60,16%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -11694,12 +11694,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>377103</t>
+          <t>376280</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>415993</t>
+          <t>415040</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -11709,12 +11709,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>56,37%</t>
+          <t>56,25%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>62,18%</t>
+          <t>62,04%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11729,12 +11729,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>768171</t>
+          <t>769176</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>832867</t>
+          <t>835461</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -11744,12 +11744,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>59,02%</t>
+          <t>59,1%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>63,99%</t>
+          <t>64,19%</t>
         </is>
       </c>
     </row>
@@ -11772,12 +11772,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>129316</t>
+          <t>128665</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>173429</t>
+          <t>172631</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -11787,12 +11787,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>27,29%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11807,12 +11807,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>161078</t>
+          <t>160394</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>195167</t>
+          <t>195715</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -11822,12 +11822,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>23,98%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>29,17%</t>
+          <t>29,26%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11842,12 +11842,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>300857</t>
+          <t>299430</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>355289</t>
+          <t>354669</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -11857,12 +11857,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>23,12%</t>
+          <t>23,01%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>27,25%</t>
         </is>
       </c>
     </row>
@@ -11885,12 +11885,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>37886</t>
+          <t>37203</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>64276</t>
+          <t>64975</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -11900,12 +11900,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11920,12 +11920,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>52693</t>
+          <t>53076</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>74976</t>
+          <t>75027</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11935,7 +11935,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -11955,12 +11955,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>94987</t>
+          <t>96064</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>130797</t>
+          <t>130682</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11970,12 +11970,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>10,04%</t>
         </is>
       </c>
     </row>
@@ -11998,12 +11998,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10533</t>
+          <t>10586</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24936</t>
+          <t>26103</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -12018,7 +12018,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -12033,12 +12033,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17399</t>
+          <t>17335</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>31485</t>
+          <t>31591</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -12048,12 +12048,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -12068,12 +12068,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>31189</t>
+          <t>31300</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>51457</t>
+          <t>50457</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -12088,7 +12088,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,88%</t>
         </is>
       </c>
     </row>
@@ -12111,12 +12111,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6247</t>
+          <t>7014</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>19648</t>
+          <t>20392</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -12126,12 +12126,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -12146,12 +12146,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>4218</t>
+          <t>4608</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>11891</t>
+          <t>12143</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -12161,12 +12161,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -12181,12 +12181,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>12855</t>
+          <t>13104</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>29019</t>
+          <t>28843</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -12196,12 +12196,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,22%</t>
         </is>
       </c>
     </row>
@@ -12341,12 +12341,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>712068</t>
+          <t>706280</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>987183</t>
+          <t>1013704</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -12356,12 +12356,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>59,85%</t>
+          <t>59,37%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>82,98%</t>
+          <t>85,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -12376,12 +12376,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>547482</t>
+          <t>544299</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>598013</t>
+          <t>593793</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -12391,12 +12391,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>57,52%</t>
+          <t>57,19%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>62,83%</t>
+          <t>62,39%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -12411,12 +12411,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1275858</t>
+          <t>1275709</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1624599</t>
+          <t>1668758</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -12426,12 +12426,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>59,58%</t>
+          <t>59,57%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>75,86%</t>
+          <t>77,93%</t>
         </is>
       </c>
     </row>
@@ -12454,12 +12454,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>139553</t>
+          <t>120184</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>337625</t>
+          <t>341669</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -12469,12 +12469,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>28,38%</t>
+          <t>28,72%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -12489,12 +12489,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>230371</t>
+          <t>229978</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>273052</t>
+          <t>276493</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -12504,12 +12504,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>24,16%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>29,05%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -12524,12 +12524,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>339058</t>
+          <t>325366</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>591114</t>
+          <t>589328</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -12539,12 +12539,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>27,52%</t>
         </is>
       </c>
     </row>
@@ -12567,12 +12567,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>34394</t>
+          <t>33538</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>91105</t>
+          <t>93354</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -12582,12 +12582,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -12602,12 +12602,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>66557</t>
+          <t>68925</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>93519</t>
+          <t>95058</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -12617,12 +12617,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -12637,12 +12637,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>98674</t>
+          <t>95094</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>175501</t>
+          <t>175290</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,19%</t>
         </is>
       </c>
     </row>
@@ -12680,12 +12680,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14261</t>
+          <t>13100</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>43673</t>
+          <t>44298</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -12695,12 +12695,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12715,12 +12715,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>26005</t>
+          <t>25537</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>44459</t>
+          <t>44086</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -12730,12 +12730,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12750,12 +12750,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>42417</t>
+          <t>41992</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>81033</t>
+          <t>80204</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -12765,12 +12765,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,75%</t>
         </is>
       </c>
     </row>
@@ -12793,12 +12793,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>7057</t>
+          <t>6796</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>62380</t>
+          <t>54723</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -12808,12 +12808,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12828,12 +12828,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>9002</t>
+          <t>9242</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>25590</t>
+          <t>27459</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -12843,12 +12843,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12863,12 +12863,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>19624</t>
+          <t>18665</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>67634</t>
+          <t>67937</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -12878,12 +12878,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,17%</t>
         </is>
       </c>
     </row>
@@ -13023,12 +13023,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>369551</t>
+          <t>369737</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>431269</t>
+          <t>431048</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -13038,12 +13038,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>52,65%</t>
+          <t>52,68%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>61,45%</t>
+          <t>61,41%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -13058,12 +13058,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>217555</t>
+          <t>205623</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>563559</t>
+          <t>564053</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -13073,12 +13073,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>22,13%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>60,66%</t>
+          <t>60,71%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -13093,12 +13093,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>530586</t>
+          <t>539633</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>964021</t>
+          <t>965416</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -13108,12 +13108,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>32,53%</t>
+          <t>33,09%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>59,11%</t>
+          <t>59,19%</t>
         </is>
       </c>
     </row>
@@ -13136,12 +13136,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>186909</t>
+          <t>186249</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>246845</t>
+          <t>244185</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -13151,12 +13151,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>26,54%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>35,17%</t>
+          <t>34,79%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -13171,12 +13171,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>110447</t>
+          <t>98868</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>269756</t>
+          <t>270065</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -13186,12 +13186,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>29,03%</t>
+          <t>29,07%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -13206,12 +13206,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>259930</t>
+          <t>250226</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>492879</t>
+          <t>495753</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -13221,12 +13221,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>30,22%</t>
+          <t>30,4%</t>
         </is>
       </c>
     </row>
@@ -13249,12 +13249,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>55943</t>
+          <t>54679</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>95371</t>
+          <t>94916</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -13264,12 +13264,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -13284,12 +13284,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>86483</t>
+          <t>87577</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>590063</t>
+          <t>623128</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -13299,12 +13299,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>63,51%</t>
+          <t>67,07%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -13319,12 +13319,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>159358</t>
+          <t>157248</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>811789</t>
+          <t>821230</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -13334,12 +13334,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>49,77%</t>
+          <t>50,35%</t>
         </is>
       </c>
     </row>
@@ -13362,12 +13362,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6746</t>
+          <t>6811</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>18306</t>
+          <t>18792</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -13377,12 +13377,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -13397,12 +13397,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5773</t>
+          <t>7008</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>23618</t>
+          <t>23983</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -13412,12 +13412,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -13432,12 +13432,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>16244</t>
+          <t>15827</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>37209</t>
+          <t>35684</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -13447,12 +13447,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,19%</t>
         </is>
       </c>
     </row>
@@ -13480,7 +13480,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>7003</t>
+          <t>6294</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -13495,7 +13495,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -13510,12 +13510,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2176</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>11463</t>
+          <t>11370</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -13525,12 +13525,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -13545,12 +13545,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3502</t>
+          <t>3899</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>13457</t>
+          <t>13509</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -13560,7 +13560,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -13705,12 +13705,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>586011</t>
+          <t>585151</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>642332</t>
+          <t>642470</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -13720,12 +13720,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>63,54%</t>
+          <t>63,45%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>69,65%</t>
+          <t>69,66%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13740,12 +13740,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>708221</t>
+          <t>704640</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>814840</t>
+          <t>805370</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -13755,12 +13755,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>65,19%</t>
+          <t>64,86%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>75,01%</t>
+          <t>74,13%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13775,12 +13775,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1311625</t>
+          <t>1310689</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1429612</t>
+          <t>1430191</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -13790,12 +13790,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>65,3%</t>
+          <t>65,25%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>71,17%</t>
+          <t>71,2%</t>
         </is>
       </c>
     </row>
@@ -13818,12 +13818,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>176910</t>
+          <t>174887</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>225482</t>
+          <t>226699</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -13833,12 +13833,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>18,96%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>24,45%</t>
+          <t>24,58%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -13853,12 +13853,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>183767</t>
+          <t>186262</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>256947</t>
+          <t>261498</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -13868,12 +13868,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>24,07%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -13888,12 +13888,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>380616</t>
+          <t>379986</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>467343</t>
+          <t>471485</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -13903,12 +13903,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>23,47%</t>
         </is>
       </c>
     </row>
@@ -13931,12 +13931,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>59924</t>
+          <t>58783</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>93493</t>
+          <t>91653</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13946,12 +13946,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13966,12 +13966,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>52373</t>
+          <t>52674</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>81635</t>
+          <t>82530</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13981,12 +13981,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -14001,12 +14001,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>120646</t>
+          <t>116924</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>166801</t>
+          <t>163439</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -14016,12 +14016,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,14%</t>
         </is>
       </c>
     </row>
@@ -14044,12 +14044,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>15377</t>
+          <t>15174</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>32355</t>
+          <t>31945</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -14079,12 +14079,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>23522</t>
+          <t>22859</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>42940</t>
+          <t>42291</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -14094,12 +14094,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -14114,12 +14114,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>43542</t>
+          <t>43303</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>66508</t>
+          <t>67869</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -14129,12 +14129,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,38%</t>
         </is>
       </c>
     </row>
@@ -14157,12 +14157,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>5651</t>
+          <t>5953</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>16878</t>
+          <t>17928</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -14172,12 +14172,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -14192,12 +14192,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>10007</t>
+          <t>10276</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>22106</t>
+          <t>22471</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -14207,12 +14207,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -14227,12 +14227,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>18024</t>
+          <t>17925</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>35093</t>
+          <t>34425</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -14242,12 +14242,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,71%</t>
         </is>
       </c>
     </row>
@@ -14387,12 +14387,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2119591</t>
+          <t>2121861</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2534312</t>
+          <t>2494307</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -14402,12 +14402,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>61,5%</t>
+          <t>61,57%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>73,54%</t>
+          <t>72,38%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -14422,12 +14422,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1751043</t>
+          <t>1772035</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2300718</t>
+          <t>2288220</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>48,16%</t>
+          <t>48,73%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>63,27%</t>
+          <t>62,93%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -14457,12 +14457,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>4011708</t>
+          <t>3992649</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4642754</t>
+          <t>4627939</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -14472,12 +14472,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>56,64%</t>
+          <t>56,37%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>65,55%</t>
+          <t>65,34%</t>
         </is>
       </c>
     </row>
@@ -14500,12 +14500,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>622451</t>
+          <t>654194</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>911117</t>
+          <t>910993</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -14515,12 +14515,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>26,43%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -14535,12 +14535,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>715040</t>
+          <t>709670</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>937246</t>
+          <t>940798</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -14550,12 +14550,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>25,78%</t>
+          <t>25,87%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -14565,17 +14565,17 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>1687313</t>
+          <t>1687312</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1467402</t>
+          <t>1453328</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1809984</t>
+          <t>1805346</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -14585,12 +14585,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>25,49%</t>
         </is>
       </c>
     </row>
@@ -14613,12 +14613,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>208396</t>
+          <t>209242</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>303929</t>
+          <t>309649</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -14628,12 +14628,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14648,12 +14648,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>292677</t>
+          <t>291394</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1106680</t>
+          <t>1033274</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -14663,12 +14663,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>30,43%</t>
+          <t>28,42%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14683,12 +14683,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>544588</t>
+          <t>544763</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1439437</t>
+          <t>1498854</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -14703,7 +14703,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>21,16%</t>
         </is>
       </c>
     </row>
@@ -14726,12 +14726,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>59746</t>
+          <t>58723</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>97708</t>
+          <t>98406</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -14741,12 +14741,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -14761,12 +14761,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>84158</t>
+          <t>83052</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>123703</t>
+          <t>122651</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -14776,12 +14776,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -14796,12 +14796,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>157750</t>
+          <t>154834</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>209977</t>
+          <t>209576</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -14811,7 +14811,7 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -14839,12 +14839,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>27729</t>
+          <t>28694</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>75812</t>
+          <t>78293</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -14854,12 +14854,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -14874,12 +14874,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>32610</t>
+          <t>32174</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>58513</t>
+          <t>58428</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -14889,7 +14889,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -14909,12 +14909,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>66880</t>
+          <t>67751</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>118697</t>
+          <t>122743</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14924,12 +14924,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,73%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P5708-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P5708-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>297025</t>
+          <t>297386</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>349270</t>
+          <t>348623</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>42,8%</t>
+          <t>42,85%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>50,33%</t>
+          <t>50,23%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>268762</t>
+          <t>273787</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>323048</t>
+          <t>323032</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,7 +783,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>39,04%</t>
+          <t>39,77%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>587672</t>
+          <t>585962</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>658436</t>
+          <t>659433</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>42,51%</t>
+          <t>42,39%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>47,63%</t>
+          <t>47,7%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>198238</t>
+          <t>199542</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>248347</t>
+          <t>247642</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>28,56%</t>
+          <t>28,75%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>35,78%</t>
+          <t>35,68%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>192273</t>
+          <t>190941</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>240465</t>
+          <t>238547</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>27,93%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>34,93%</t>
+          <t>34,65%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>405841</t>
+          <t>405214</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>472240</t>
+          <t>472959</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>29,31%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>34,16%</t>
+          <t>34,21%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>107072</t>
+          <t>108608</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>147737</t>
+          <t>148637</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>115272</t>
+          <t>116363</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>159441</t>
+          <t>158427</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>23,16%</t>
+          <t>23,02%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>237619</t>
+          <t>238763</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>291995</t>
+          <t>295890</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>21,4%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11625</t>
+          <t>11064</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>29693</t>
+          <t>29783</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>25708</t>
+          <t>25277</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>49298</t>
+          <t>48556</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>41539</t>
+          <t>41922</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>72231</t>
+          <t>72654</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,26%</t>
         </is>
       </c>
     </row>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4852</t>
+          <t>5500</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1205,7 +1205,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>795</t>
+          <t>799</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>8412</t>
+          <t>8460</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1240,7 +1240,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>1078</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>9683</t>
+          <t>9662</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>509983</t>
+          <t>509149</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>573140</t>
+          <t>572250</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>53,02%</t>
+          <t>52,94%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>59,59%</t>
+          <t>59,5%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>508417</t>
+          <t>506014</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>571623</t>
+          <t>571135</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>52,5%</t>
+          <t>52,25%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>59,03%</t>
+          <t>58,98%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1033376</t>
+          <t>1032962</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1118277</t>
+          <t>1123927</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>53,54%</t>
+          <t>53,52%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>57,94%</t>
+          <t>58,23%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>227867</t>
+          <t>230383</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>284696</t>
+          <t>284254</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>23,95%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>29,6%</t>
+          <t>29,55%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>232486</t>
+          <t>232173</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>287694</t>
+          <t>288659</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>24,01%</t>
+          <t>23,98%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>29,71%</t>
+          <t>29,81%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>481507</t>
+          <t>480300</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>559557</t>
+          <t>555643</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>28,99%</t>
+          <t>28,79%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>116545</t>
+          <t>118811</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>161742</t>
+          <t>165233</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>126594</t>
+          <t>125398</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>173294</t>
+          <t>169590</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>252818</t>
+          <t>253341</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>315391</t>
+          <t>318490</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,5%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13694</t>
+          <t>13166</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>33621</t>
+          <t>31230</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11997</t>
+          <t>11795</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>31068</t>
+          <t>30481</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>30419</t>
+          <t>29567</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>57005</t>
+          <t>55061</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,85%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1965</t>
+          <t>1964</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>11789</t>
+          <t>11968</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>968</t>
+          <t>972</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>8070</t>
+          <t>8451</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3377</t>
+          <t>3619</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>15718</t>
+          <t>14830</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,77%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>379096</t>
+          <t>381568</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>430900</t>
+          <t>432047</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>55,87%</t>
+          <t>56,24%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>63,51%</t>
+          <t>63,68%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>396253</t>
+          <t>393069</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>446076</t>
+          <t>442174</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>57,95%</t>
+          <t>57,48%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>65,23%</t>
+          <t>64,66%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>790546</t>
+          <t>788182</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>863080</t>
+          <t>862558</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>58,03%</t>
+          <t>57,85%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>63,35%</t>
+          <t>63,31%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>147231</t>
+          <t>147791</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>194677</t>
+          <t>192504</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>28,37%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>127126</t>
+          <t>126710</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>168785</t>
+          <t>166995</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>284870</t>
+          <t>284501</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>346023</t>
+          <t>347102</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>20,88%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>25,48%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>63959</t>
+          <t>64561</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>99890</t>
+          <t>98640</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>73120</t>
+          <t>71325</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>107195</t>
+          <t>107481</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>147978</t>
+          <t>146745</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>195547</t>
+          <t>195393</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,34%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11470</t>
+          <t>11548</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>30438</t>
+          <t>29251</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>16942</t>
+          <t>17153</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>39181</t>
+          <t>38133</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>32612</t>
+          <t>33201</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>59738</t>
+          <t>60507</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,44%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>920</t>
+          <t>937</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>9854</t>
+          <t>11188</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2569,7 +2569,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>922</t>
+          <t>914</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>8471</t>
+          <t>8051</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2144</t>
+          <t>2697</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>13483</t>
+          <t>14088</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,03%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>493957</t>
+          <t>492944</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>555636</t>
+          <t>553713</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>52,51%</t>
+          <t>52,4%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>59,07%</t>
+          <t>58,86%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>548304</t>
+          <t>550330</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>612103</t>
+          <t>613810</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>52,84%</t>
+          <t>53,04%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>58,99%</t>
+          <t>59,15%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1063402</t>
+          <t>1063549</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1145666</t>
+          <t>1152858</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>53,75%</t>
+          <t>53,76%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>57,91%</t>
+          <t>58,28%</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>235207</t>
+          <t>235489</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>290258</t>
+          <t>290746</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2907,12 +2907,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>25,03%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>30,86%</t>
+          <t>30,91%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>212753</t>
+          <t>211750</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>267050</t>
+          <t>264818</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>25,52%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>462954</t>
+          <t>461778</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>537403</t>
+          <t>537985</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>23,34%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>27,19%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>94872</t>
+          <t>94428</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>134645</t>
+          <t>132285</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>130577</t>
+          <t>131008</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>174775</t>
+          <t>177321</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>235177</t>
+          <t>237796</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>297619</t>
+          <t>295839</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>14,95%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>29297</t>
+          <t>29848</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>55695</t>
+          <t>54352</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>42775</t>
+          <t>43542</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>71686</t>
+          <t>74896</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>78627</t>
+          <t>78465</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>118095</t>
+          <t>117813</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3208,7 +3208,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,96%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>876</t>
+          <t>838</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>8400</t>
+          <t>9022</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>4439</t>
+          <t>4090</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>17064</t>
+          <t>16009</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6556</t>
+          <t>6432</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>20688</t>
+          <t>20853</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3461,12 +3461,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1734981</t>
+          <t>1735010</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1851462</t>
+          <t>1851492</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1781930</t>
+          <t>1781648</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1896253</t>
+          <t>1896141</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>52,75%</t>
+          <t>52,74%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3547712</t>
+          <t>3551844</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3710601</t>
+          <t>3718054</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>53,32%</t>
+          <t>53,39%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>55,77%</t>
+          <t>55,88%</t>
         </is>
       </c>
     </row>
@@ -3574,12 +3574,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>858890</t>
+          <t>860556</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>962178</t>
+          <t>968126</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3589,12 +3589,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>26,28%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>29,38%</t>
+          <t>29,56%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3609,12 +3609,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>805817</t>
+          <t>808400</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>913691</t>
+          <t>907610</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>27,05%</t>
+          <t>26,87%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3644,12 +3644,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1691308</t>
+          <t>1698148</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1837214</t>
+          <t>1840295</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>25,52%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>27,61%</t>
+          <t>27,66%</t>
         </is>
       </c>
     </row>
@@ -3687,12 +3687,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>420871</t>
+          <t>424127</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>500447</t>
+          <t>502512</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3702,12 +3702,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3722,12 +3722,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>483733</t>
+          <t>478877</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>569322</t>
+          <t>568429</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3737,12 +3737,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3757,12 +3757,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>928719</t>
+          <t>926567</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1043851</t>
+          <t>1044738</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3772,12 +3772,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,7%</t>
         </is>
       </c>
     </row>
@@ -3800,12 +3800,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>82329</t>
+          <t>82429</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>122619</t>
+          <t>122350</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3815,7 +3815,7 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>116761</t>
+          <t>116894</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>163781</t>
+          <t>163897</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>211282</t>
+          <t>211162</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>272309</t>
+          <t>274099</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3885,12 +3885,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,12%</t>
         </is>
       </c>
     </row>
@@ -3913,12 +3913,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>7325</t>
+          <t>6466</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>20926</t>
+          <t>21466</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3928,12 +3928,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>10581</t>
+          <t>10612</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>29180</t>
+          <t>27561</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3968,7 +3968,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3983,12 +3983,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>21145</t>
+          <t>20591</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>42690</t>
+          <t>42103</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3998,12 +3998,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,63%</t>
         </is>
       </c>
     </row>
@@ -4375,12 +4375,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>425714</t>
+          <t>425572</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>477532</t>
+          <t>477934</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4390,12 +4390,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>60,85%</t>
+          <t>60,83%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>68,26%</t>
+          <t>68,32%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>389589</t>
+          <t>389028</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>443005</t>
+          <t>442621</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4425,12 +4425,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>55,89%</t>
+          <t>55,81%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>63,55%</t>
+          <t>63,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>832809</t>
+          <t>832464</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>906465</t>
+          <t>910536</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4460,12 +4460,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>59,63%</t>
+          <t>59,61%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>64,9%</t>
+          <t>65,2%</t>
         </is>
       </c>
     </row>
@@ -4488,12 +4488,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>153979</t>
+          <t>154453</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>200610</t>
+          <t>201162</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4503,12 +4503,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>22,08%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,68%</t>
+          <t>28,75%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4523,12 +4523,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>178876</t>
+          <t>177750</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>226403</t>
+          <t>228154</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4538,12 +4538,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>25,5%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>32,48%</t>
+          <t>32,73%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4558,12 +4558,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>343824</t>
+          <t>341095</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>411028</t>
+          <t>412342</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4573,12 +4573,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>29,52%</t>
         </is>
       </c>
     </row>
@@ -4601,12 +4601,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>39545</t>
+          <t>38410</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>67565</t>
+          <t>66900</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4616,12 +4616,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4636,12 +4636,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>38666</t>
+          <t>37559</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>67210</t>
+          <t>68065</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4671,12 +4671,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>84629</t>
+          <t>85775</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>124044</t>
+          <t>126124</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4686,12 +4686,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>9,03%</t>
         </is>
       </c>
     </row>
@@ -4714,12 +4714,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7433</t>
+          <t>7552</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21718</t>
+          <t>22722</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4729,12 +4729,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4749,12 +4749,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12615</t>
+          <t>12327</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>31979</t>
+          <t>32442</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4764,12 +4764,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4784,12 +4784,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>23838</t>
+          <t>22435</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>48398</t>
+          <t>46591</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4799,12 +4799,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,34%</t>
         </is>
       </c>
     </row>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1904</t>
+          <t>2136</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>12099</t>
+          <t>11808</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4842,12 +4842,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4862,12 +4862,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1918</t>
+          <t>1927</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>11366</t>
+          <t>11345</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4897,12 +4897,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>5713</t>
+          <t>5746</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>18362</t>
+          <t>18480</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4917,7 +4917,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,32%</t>
         </is>
       </c>
     </row>
@@ -5057,12 +5057,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>577625</t>
+          <t>577059</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>643401</t>
+          <t>643204</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5072,12 +5072,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>57,17%</t>
+          <t>57,11%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>63,67%</t>
+          <t>63,66%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5092,12 +5092,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>539270</t>
+          <t>539039</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>605800</t>
+          <t>606593</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5107,12 +5107,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>52,35%</t>
+          <t>52,33%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>58,81%</t>
+          <t>58,89%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5127,12 +5127,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1131438</t>
+          <t>1135394</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1223680</t>
+          <t>1226938</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5142,12 +5142,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>55,45%</t>
+          <t>55,64%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>59,97%</t>
+          <t>60,13%</t>
         </is>
       </c>
     </row>
@@ -5170,12 +5170,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>227627</t>
+          <t>225838</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>284870</t>
+          <t>284966</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5185,12 +5185,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>22,53%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>28,19%</t>
+          <t>28,2%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5205,12 +5205,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>300197</t>
+          <t>299400</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>363938</t>
+          <t>363728</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5220,12 +5220,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>29,06%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>35,33%</t>
+          <t>35,31%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5240,12 +5240,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>548603</t>
+          <t>543146</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>629451</t>
+          <t>628765</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5255,12 +5255,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>26,88%</t>
+          <t>26,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>30,81%</t>
         </is>
       </c>
     </row>
@@ -5283,12 +5283,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>88377</t>
+          <t>87387</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>128029</t>
+          <t>127497</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5298,12 +5298,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5318,12 +5318,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>84817</t>
+          <t>83874</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>124756</t>
+          <t>124478</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5353,12 +5353,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>181302</t>
+          <t>182954</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>239201</t>
+          <t>241293</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,82%</t>
         </is>
       </c>
     </row>
@@ -5396,12 +5396,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>23206</t>
+          <t>23058</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>48079</t>
+          <t>47780</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5411,12 +5411,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5431,12 +5431,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10285</t>
+          <t>10468</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>28712</t>
+          <t>29043</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5446,12 +5446,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5466,12 +5466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>39299</t>
+          <t>38290</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>70269</t>
+          <t>68896</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5481,12 +5481,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,38%</t>
         </is>
       </c>
     </row>
@@ -5509,12 +5509,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1132</t>
+          <t>1046</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>10506</t>
+          <t>10582</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5524,12 +5524,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5544,12 +5544,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1861</t>
+          <t>1872</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>14807</t>
+          <t>16105</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5564,7 +5564,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5579,12 +5579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4220</t>
+          <t>4327</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>20623</t>
+          <t>20924</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5599,7 +5599,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,03%</t>
         </is>
       </c>
     </row>
@@ -5739,12 +5739,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>424400</t>
+          <t>419592</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>479144</t>
+          <t>476310</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5754,12 +5754,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>56,35%</t>
+          <t>55,71%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>63,61%</t>
+          <t>63,24%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5774,12 +5774,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>427536</t>
+          <t>428994</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>483503</t>
+          <t>485700</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>55,01%</t>
+          <t>55,2%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>62,21%</t>
+          <t>62,5%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5809,12 +5809,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>863406</t>
+          <t>866862</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>946343</t>
+          <t>945341</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>56,42%</t>
+          <t>56,64%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>61,84%</t>
+          <t>61,77%</t>
         </is>
       </c>
     </row>
@@ -5852,12 +5852,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>166566</t>
+          <t>165483</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>212504</t>
+          <t>218075</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5867,12 +5867,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>21,97%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>28,95%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5887,12 +5887,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>182352</t>
+          <t>184890</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>236169</t>
+          <t>236559</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5902,12 +5902,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>23,79%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>30,39%</t>
+          <t>30,44%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5922,12 +5922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>364267</t>
+          <t>364956</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>436632</t>
+          <t>435574</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5937,12 +5937,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>23,85%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>28,53%</t>
+          <t>28,46%</t>
         </is>
       </c>
     </row>
@@ -5965,12 +5965,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>69714</t>
+          <t>72018</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>111227</t>
+          <t>111788</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5980,12 +5980,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6000,12 +6000,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>67250</t>
+          <t>65605</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>103483</t>
+          <t>102143</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6015,12 +6015,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6035,12 +6035,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>149339</t>
+          <t>147543</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>202496</t>
+          <t>201611</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>13,17%</t>
         </is>
       </c>
     </row>
@@ -6078,12 +6078,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7095</t>
+          <t>7988</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>21769</t>
+          <t>22232</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6093,12 +6093,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>11752</t>
+          <t>11295</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>30812</t>
+          <t>30325</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>22666</t>
+          <t>22178</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>45438</t>
+          <t>46185</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,02%</t>
         </is>
       </c>
     </row>
@@ -6191,12 +6191,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3861</t>
+          <t>3633</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>18433</t>
+          <t>17062</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6206,12 +6206,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>4011</t>
+          <t>4006</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>16123</t>
+          <t>16322</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6246,7 +6246,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>9756</t>
+          <t>10049</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>28376</t>
+          <t>27659</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,81%</t>
         </is>
       </c>
     </row>
@@ -6421,12 +6421,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>502726</t>
+          <t>503324</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>563860</t>
+          <t>564416</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6436,12 +6436,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>53,23%</t>
+          <t>53,29%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>59,7%</t>
+          <t>59,76%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>527841</t>
+          <t>525619</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>593341</t>
+          <t>594607</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>50,38%</t>
+          <t>50,16%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>56,63%</t>
+          <t>56,75%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1043259</t>
+          <t>1054144</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1142569</t>
+          <t>1147902</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>52,36%</t>
+          <t>52,91%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>57,35%</t>
+          <t>57,62%</t>
         </is>
       </c>
     </row>
@@ -6534,12 +6534,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>243849</t>
+          <t>243262</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>301726</t>
+          <t>297808</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6549,12 +6549,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>25,75%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>31,94%</t>
+          <t>31,53%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6569,12 +6569,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>302076</t>
+          <t>301259</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>365586</t>
+          <t>363953</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6584,12 +6584,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>28,83%</t>
+          <t>28,75%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>34,89%</t>
+          <t>34,73%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>559810</t>
+          <t>554488</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>644836</t>
+          <t>640498</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6619,12 +6619,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>27,83%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>32,37%</t>
+          <t>32,15%</t>
         </is>
       </c>
     </row>
@@ -6647,12 +6647,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>92931</t>
+          <t>92057</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>134725</t>
+          <t>133298</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6662,12 +6662,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6682,12 +6682,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>101676</t>
+          <t>101129</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>145095</t>
+          <t>143867</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6697,12 +6697,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6717,12 +6717,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>204159</t>
+          <t>207717</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>263890</t>
+          <t>264104</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6732,12 +6732,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,26%</t>
         </is>
       </c>
     </row>
@@ -6760,12 +6760,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>13703</t>
+          <t>14048</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>32035</t>
+          <t>31766</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6775,82 +6775,82 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
+          <t>1,49%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>3,36%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>18963</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>12136</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>28813</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>1,81%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>1,16%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>2,75%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>40572</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>28850</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>55304</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>2,04%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
           <t>1,45%</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>3,39%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>18963</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>11798</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>29807</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>1,81%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>1,13%</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>2,84%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>40572</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>29375</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>55194</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>2,04%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>1,47%</t>
-        </is>
-      </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,78%</t>
         </is>
       </c>
     </row>
@@ -6873,12 +6873,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1983</t>
+          <t>2314</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>12948</t>
+          <t>13065</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6888,12 +6888,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6908,12 +6908,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>8139</t>
+          <t>8547</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>26003</t>
+          <t>25674</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6923,12 +6923,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6943,12 +6943,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>12539</t>
+          <t>13012</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>31368</t>
+          <t>32602</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6958,12 +6958,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,64%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1991753</t>
+          <t>1992551</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2104322</t>
+          <t>2108234</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>58,45%</t>
+          <t>58,47%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>61,75%</t>
+          <t>61,87%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1942758</t>
+          <t>1949043</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2064292</t>
+          <t>2069282</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7153,12 +7153,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>54,69%</t>
+          <t>54,87%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>58,11%</t>
+          <t>58,25%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3969442</t>
+          <t>3969192</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4144682</t>
+          <t>4137981</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7193,7 +7193,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>59,55%</t>
+          <t>59,45%</t>
         </is>
       </c>
     </row>
@@ -7216,12 +7216,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>839091</t>
+          <t>838937</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>941095</t>
+          <t>946391</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7236,7 +7236,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>27,77%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7251,12 +7251,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1017254</t>
+          <t>1019165</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1130641</t>
+          <t>1128988</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7266,12 +7266,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>28,69%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>31,83%</t>
+          <t>31,78%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1878093</t>
+          <t>1887790</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2044452</t>
+          <t>2037769</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7301,12 +7301,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>27,12%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>29,28%</t>
         </is>
       </c>
     </row>
@@ -7329,12 +7329,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>326038</t>
+          <t>325221</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>401073</t>
+          <t>400727</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7344,12 +7344,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7364,12 +7364,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>326027</t>
+          <t>327319</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>399961</t>
+          <t>400259</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7379,12 +7379,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7399,12 +7399,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>668817</t>
+          <t>669974</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>776996</t>
+          <t>777881</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,18%</t>
         </is>
       </c>
     </row>
@@ -7442,12 +7442,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>63876</t>
+          <t>65096</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>100733</t>
+          <t>101312</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7457,12 +7457,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7477,12 +7477,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>60878</t>
+          <t>61111</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>95959</t>
+          <t>97871</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7492,12 +7492,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>134536</t>
+          <t>134333</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>187632</t>
+          <t>190456</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7532,7 +7532,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,74%</t>
         </is>
       </c>
     </row>
@@ -7555,12 +7555,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>16035</t>
+          <t>15572</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>38674</t>
+          <t>36287</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7570,12 +7570,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7590,12 +7590,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>23539</t>
+          <t>23064</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>48216</t>
+          <t>49726</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7605,12 +7605,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7625,12 +7625,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>44099</t>
+          <t>45037</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>77962</t>
+          <t>75752</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7640,12 +7640,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,09%</t>
         </is>
       </c>
     </row>
@@ -8017,12 +8017,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>311697</t>
+          <t>311319</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>363700</t>
+          <t>363370</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8032,12 +8032,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>46,34%</t>
+          <t>46,28%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>54,07%</t>
+          <t>54,02%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>297530</t>
+          <t>294162</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>347402</t>
+          <t>350708</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8067,12 +8067,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>44,35%</t>
+          <t>43,85%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>51,78%</t>
+          <t>52,28%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8087,12 +8087,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>617275</t>
+          <t>623837</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>691551</t>
+          <t>695755</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8102,12 +8102,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>45,94%</t>
+          <t>46,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>51,47%</t>
+          <t>51,79%</t>
         </is>
       </c>
     </row>
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>195944</t>
+          <t>197567</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>244662</t>
+          <t>245801</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8145,12 +8145,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>29,37%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>36,37%</t>
+          <t>36,54%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8165,12 +8165,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>203051</t>
+          <t>203368</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>251061</t>
+          <t>252318</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8180,12 +8180,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>30,27%</t>
+          <t>30,31%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>37,42%</t>
+          <t>37,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8200,12 +8200,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>416838</t>
+          <t>412251</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>485274</t>
+          <t>484398</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8215,12 +8215,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>31,03%</t>
+          <t>30,68%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>36,12%</t>
+          <t>36,05%</t>
         </is>
       </c>
     </row>
@@ -8243,12 +8243,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>72116</t>
+          <t>71480</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>106935</t>
+          <t>105390</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8258,12 +8258,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8278,12 +8278,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>82044</t>
+          <t>82186</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>116056</t>
+          <t>117554</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8293,12 +8293,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8313,12 +8313,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>161906</t>
+          <t>164612</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>214442</t>
+          <t>214076</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8328,12 +8328,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>15,93%</t>
         </is>
       </c>
     </row>
@@ -8356,12 +8356,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14185</t>
+          <t>15256</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>35085</t>
+          <t>34133</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8371,12 +8371,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8391,12 +8391,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9235</t>
+          <t>9714</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>27635</t>
+          <t>26698</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8406,12 +8406,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8426,12 +8426,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>27838</t>
+          <t>26677</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>53322</t>
+          <t>52807</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,93%</t>
         </is>
       </c>
     </row>
@@ -8469,12 +8469,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>998</t>
+          <t>995</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8989</t>
+          <t>8838</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8489,7 +8489,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8504,12 +8504,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2175</t>
+          <t>2090</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>13212</t>
+          <t>13201</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8519,7 +8519,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -8539,12 +8539,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4248</t>
+          <t>4076</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>17129</t>
+          <t>17424</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,3%</t>
         </is>
       </c>
     </row>
@@ -8699,12 +8699,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>522492</t>
+          <t>523412</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>588633</t>
+          <t>586906</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8714,12 +8714,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>51,31%</t>
+          <t>51,4%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>57,8%</t>
+          <t>57,63%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8734,12 +8734,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>527353</t>
+          <t>528256</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>592767</t>
+          <t>594606</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8749,12 +8749,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>50,61%</t>
+          <t>50,7%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>56,89%</t>
+          <t>57,07%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8769,12 +8769,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1064085</t>
+          <t>1071723</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1158811</t>
+          <t>1162217</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>51,65%</t>
+          <t>52,02%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>56,25%</t>
+          <t>56,41%</t>
         </is>
       </c>
     </row>
@@ -8812,12 +8812,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>277009</t>
+          <t>277967</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>337434</t>
+          <t>338959</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8827,12 +8827,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>27,2%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>33,14%</t>
+          <t>33,29%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8847,12 +8847,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>292694</t>
+          <t>296373</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>356415</t>
+          <t>357773</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8862,12 +8862,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>28,45%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>34,21%</t>
+          <t>34,34%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8882,12 +8882,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>594008</t>
+          <t>591226</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>678687</t>
+          <t>678822</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>28,83%</t>
+          <t>28,7%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>32,94%</t>
+          <t>32,95%</t>
         </is>
       </c>
     </row>
@@ -8925,12 +8925,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>112862</t>
+          <t>114418</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>156071</t>
+          <t>159356</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8940,12 +8940,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8960,12 +8960,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>114403</t>
+          <t>113920</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>159074</t>
+          <t>158270</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8975,12 +8975,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>238063</t>
+          <t>239200</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>304057</t>
+          <t>301468</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9010,12 +9010,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>14,63%</t>
         </is>
       </c>
     </row>
@@ -9038,12 +9038,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9041</t>
+          <t>9627</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26211</t>
+          <t>26563</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9073,12 +9073,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7352</t>
+          <t>7502</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>24835</t>
+          <t>25045</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9088,12 +9088,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9108,12 +9108,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>19381</t>
+          <t>19582</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>43879</t>
+          <t>42719</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9123,12 +9123,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,07%</t>
         </is>
       </c>
     </row>
@@ -9151,12 +9151,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1814</t>
+          <t>1883</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>11174</t>
+          <t>11945</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9171,7 +9171,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9186,12 +9186,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2994</t>
+          <t>2927</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>15429</t>
+          <t>15131</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6070</t>
+          <t>6454</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>21034</t>
+          <t>21923</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9236,12 +9236,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,06%</t>
         </is>
       </c>
     </row>
@@ -9381,12 +9381,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>284998</t>
+          <t>286560</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>340903</t>
+          <t>343373</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9396,12 +9396,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>37,7%</t>
+          <t>37,91%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>45,1%</t>
+          <t>45,43%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9416,12 +9416,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>280263</t>
+          <t>280149</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>337614</t>
+          <t>337020</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>36,07%</t>
+          <t>36,06%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>43,46%</t>
+          <t>43,38%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9451,12 +9451,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>586986</t>
+          <t>584952</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>666108</t>
+          <t>662687</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9466,12 +9466,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>38,29%</t>
+          <t>38,16%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>43,46%</t>
+          <t>43,23%</t>
         </is>
       </c>
     </row>
@@ -9494,12 +9494,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>238052</t>
+          <t>234909</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>287836</t>
+          <t>291592</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9509,12 +9509,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>31,49%</t>
+          <t>31,08%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>38,08%</t>
+          <t>38,58%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9529,12 +9529,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>263070</t>
+          <t>264097</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>319546</t>
+          <t>317402</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>33,86%</t>
+          <t>33,99%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>41,13%</t>
+          <t>40,85%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9564,12 +9564,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>515026</t>
+          <t>520732</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>589397</t>
+          <t>596569</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9579,12 +9579,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>33,6%</t>
+          <t>33,97%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>38,45%</t>
+          <t>38,92%</t>
         </is>
       </c>
     </row>
@@ -9607,12 +9607,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>142657</t>
+          <t>141674</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>188993</t>
+          <t>191771</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9622,12 +9622,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>25,37%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9642,12 +9642,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>134588</t>
+          <t>133775</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>183416</t>
+          <t>181051</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9657,12 +9657,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>23,3%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>293620</t>
+          <t>291657</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>362560</t>
+          <t>357395</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9692,12 +9692,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>23,32%</t>
         </is>
       </c>
     </row>
@@ -9720,12 +9720,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4557</t>
+          <t>5106</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>18523</t>
+          <t>18658</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9735,12 +9735,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>9753</t>
+          <t>9812</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>27273</t>
+          <t>27234</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9790,12 +9790,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>17073</t>
+          <t>17162</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>39679</t>
+          <t>38645</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9805,12 +9805,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,52%</t>
         </is>
       </c>
     </row>
@@ -9838,7 +9838,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>8652</t>
+          <t>8693</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9853,7 +9853,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9873,7 +9873,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>6840</t>
+          <t>6355</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9888,7 +9888,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9903,12 +9903,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1440</t>
+          <t>1081</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>11827</t>
+          <t>11066</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9918,12 +9918,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,72%</t>
         </is>
       </c>
     </row>
@@ -10063,12 +10063,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>464668</t>
+          <t>465727</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>525377</t>
+          <t>527157</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10078,12 +10078,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>49,68%</t>
+          <t>49,79%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>56,17%</t>
+          <t>56,36%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>535797</t>
+          <t>534020</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>603155</t>
+          <t>600423</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10113,12 +10113,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>51,41%</t>
+          <t>51,24%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>57,88%</t>
+          <t>57,62%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10133,12 +10133,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1017887</t>
+          <t>1017066</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1103306</t>
+          <t>1111143</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10148,12 +10148,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>51,48%</t>
+          <t>51,43%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>55,8%</t>
+          <t>56,19%</t>
         </is>
       </c>
     </row>
@@ -10176,12 +10176,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>259455</t>
+          <t>259529</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>314792</t>
+          <t>316954</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10191,12 +10191,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>27,75%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>33,66%</t>
+          <t>33,89%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>271373</t>
+          <t>270135</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>331888</t>
+          <t>330997</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10226,12 +10226,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>26,04%</t>
+          <t>25,92%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>31,85%</t>
+          <t>31,76%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10246,12 +10246,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>550297</t>
+          <t>542130</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>629499</t>
+          <t>626030</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10261,12 +10261,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>27,42%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>31,83%</t>
+          <t>31,66%</t>
         </is>
       </c>
     </row>
@@ -10289,12 +10289,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>109272</t>
+          <t>108133</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>149500</t>
+          <t>149558</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10304,12 +10304,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10324,12 +10324,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>107733</t>
+          <t>111869</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>154752</t>
+          <t>156965</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10339,12 +10339,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10359,12 +10359,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>226191</t>
+          <t>225976</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>288529</t>
+          <t>289485</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10374,12 +10374,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,64%</t>
         </is>
       </c>
     </row>
@@ -10402,12 +10402,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>9045</t>
+          <t>9656</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>25947</t>
+          <t>26261</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10417,12 +10417,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10437,12 +10437,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>25813</t>
+          <t>24755</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>49288</t>
+          <t>49350</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10452,12 +10452,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10472,12 +10472,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>40499</t>
+          <t>38602</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>70404</t>
+          <t>71178</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10487,12 +10487,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,6%</t>
         </is>
       </c>
     </row>
@@ -10515,12 +10515,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3483</t>
+          <t>4158</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>15797</t>
+          <t>16720</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10530,12 +10530,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10550,12 +10550,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2687</t>
+          <t>3099</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>14947</t>
+          <t>15746</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10565,12 +10565,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10585,12 +10585,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>9090</t>
+          <t>8105</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>26386</t>
+          <t>25710</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10600,12 +10600,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,3%</t>
         </is>
       </c>
     </row>
@@ -10745,12 +10745,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1647619</t>
+          <t>1650189</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1763715</t>
+          <t>1759898</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10760,12 +10760,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>48,71%</t>
+          <t>48,79%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>52,15%</t>
+          <t>52,03%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10780,12 +10780,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1693232</t>
+          <t>1695872</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1817535</t>
+          <t>1820662</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10795,12 +10795,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>47,94%</t>
+          <t>48,02%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>51,46%</t>
+          <t>51,55%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10815,12 +10815,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3373147</t>
+          <t>3376841</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3544588</t>
+          <t>3543613</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>48,79%</t>
+          <t>48,84%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>51,27%</t>
+          <t>51,25%</t>
         </is>
       </c>
     </row>
@@ -10858,12 +10858,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1021559</t>
+          <t>1028303</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1127751</t>
+          <t>1137310</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10873,12 +10873,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>30,2%</t>
+          <t>30,4%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>33,34%</t>
+          <t>33,63%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10893,12 +10893,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1088881</t>
+          <t>1090436</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1205985</t>
+          <t>1208762</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10908,12 +10908,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>30,87%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>34,15%</t>
+          <t>34,23%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10928,12 +10928,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2150129</t>
+          <t>2147182</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2307743</t>
+          <t>2297280</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10943,12 +10943,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>31,1%</t>
+          <t>31,06%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>33,38%</t>
+          <t>33,23%</t>
         </is>
       </c>
     </row>
@@ -10971,12 +10971,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>471769</t>
+          <t>472974</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>562355</t>
+          <t>558571</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11006,12 +11006,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>481154</t>
+          <t>482009</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>570597</t>
+          <t>565359</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11021,12 +11021,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11041,12 +11041,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>986255</t>
+          <t>976090</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1109204</t>
+          <t>1098730</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11056,12 +11056,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>15,89%</t>
         </is>
       </c>
     </row>
@@ -11084,12 +11084,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>50315</t>
+          <t>50766</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>83969</t>
+          <t>84647</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11099,12 +11099,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11119,12 +11119,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>64402</t>
+          <t>67094</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>100609</t>
+          <t>104535</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11134,12 +11134,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11154,12 +11154,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>125514</t>
+          <t>124787</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>177678</t>
+          <t>176800</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11169,12 +11169,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,56%</t>
         </is>
       </c>
     </row>
@@ -11197,12 +11197,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>11624</t>
+          <t>12009</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>30683</t>
+          <t>30754</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11212,7 +11212,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -11232,12 +11232,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>14152</t>
+          <t>13877</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>33679</t>
+          <t>33778</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11247,12 +11247,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11267,12 +11267,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>29761</t>
+          <t>28585</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>56874</t>
+          <t>55559</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11282,12 +11282,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,8%</t>
         </is>
       </c>
     </row>
@@ -11654,32 +11654,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>405685</t>
+          <t>431167</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>380486</t>
+          <t>405900</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>430932</t>
+          <t>458074</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>64,14%</t>
+          <t>62,7%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>60,16%</t>
+          <t>59,03%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>68,13%</t>
+          <t>66,61%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11689,32 +11689,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>396318</t>
+          <t>429426</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>376280</t>
+          <t>408043</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>415040</t>
+          <t>450661</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>59,24%</t>
+          <t>59,14%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>56,25%</t>
+          <t>56,19%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>62,04%</t>
+          <t>62,06%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11724,32 +11724,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>802002</t>
+          <t>860593</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>769176</t>
+          <t>828518</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>835461</t>
+          <t>895256</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>61,62%</t>
+          <t>60,87%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>59,1%</t>
+          <t>58,6%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>64,19%</t>
+          <t>63,32%</t>
         </is>
       </c>
     </row>
@@ -11767,32 +11767,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>148873</t>
+          <t>164709</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>128665</t>
+          <t>143048</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>172631</t>
+          <t>189975</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>23,95%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>20,8%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>27,29%</t>
+          <t>27,63%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11802,17 +11802,17 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>178479</t>
+          <t>193777</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>160394</t>
+          <t>176478</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>195715</t>
+          <t>212853</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -11822,12 +11822,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>29,26%</t>
+          <t>29,31%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11837,32 +11837,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>327352</t>
+          <t>358487</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>299430</t>
+          <t>329232</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>354669</t>
+          <t>388603</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>25,36%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>27,25%</t>
+          <t>27,49%</t>
         </is>
       </c>
     </row>
@@ -11880,32 +11880,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>49321</t>
+          <t>57702</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>37203</t>
+          <t>44163</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>64975</t>
+          <t>74803</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11915,32 +11915,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>63138</t>
+          <t>68657</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>53076</t>
+          <t>57991</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>75027</t>
+          <t>81561</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11950,32 +11950,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>112459</t>
+          <t>126358</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>96064</t>
+          <t>108462</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>130682</t>
+          <t>146998</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,4%</t>
         </is>
       </c>
     </row>
@@ -11993,32 +11993,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>16714</t>
+          <t>19399</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10586</t>
+          <t>11952</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26103</t>
+          <t>29163</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -12028,32 +12028,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>23545</t>
+          <t>25341</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17335</t>
+          <t>18240</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>31591</t>
+          <t>34554</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -12063,32 +12063,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>40259</t>
+          <t>44740</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>31300</t>
+          <t>35190</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>50457</t>
+          <t>59003</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>4,17%</t>
         </is>
       </c>
     </row>
@@ -12106,32 +12106,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>11911</t>
+          <t>14670</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7014</t>
+          <t>8313</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>20392</t>
+          <t>25611</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -12141,32 +12141,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>7510</t>
+          <t>8966</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>4608</t>
+          <t>5495</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>12143</t>
+          <t>14262</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -12176,32 +12176,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>19420</t>
+          <t>23635</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>13104</t>
+          <t>16290</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>28843</t>
+          <t>33203</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,35%</t>
         </is>
       </c>
     </row>
@@ -12219,17 +12219,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>632503</t>
+          <t>687647</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>632503</t>
+          <t>687647</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>632503</t>
+          <t>687647</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -12254,17 +12254,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>668989</t>
+          <t>726167</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>668989</t>
+          <t>726167</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>668989</t>
+          <t>726167</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -12289,17 +12289,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1301492</t>
+          <t>1413814</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1301492</t>
+          <t>1413814</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1301492</t>
+          <t>1413814</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -12336,32 +12336,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>817410</t>
+          <t>630905</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>706280</t>
+          <t>595246</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1013704</t>
+          <t>668815</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>68,71%</t>
+          <t>60,43%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>59,37%</t>
+          <t>57,02%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>85,21%</t>
+          <t>64,06%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -12371,32 +12371,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>570267</t>
+          <t>626600</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>544299</t>
+          <t>599524</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>593793</t>
+          <t>656227</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>59,92%</t>
+          <t>58,87%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>57,19%</t>
+          <t>56,33%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>62,39%</t>
+          <t>61,65%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -12406,32 +12406,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>1387676</t>
+          <t>1257505</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1275709</t>
+          <t>1210321</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1668758</t>
+          <t>1301621</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>64,8%</t>
+          <t>59,64%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>59,57%</t>
+          <t>57,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>77,93%</t>
+          <t>61,74%</t>
         </is>
       </c>
     </row>
@@ -12449,32 +12449,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>258590</t>
+          <t>289802</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>120184</t>
+          <t>256652</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>341669</t>
+          <t>322940</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>27,76%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>24,58%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>28,72%</t>
+          <t>30,93%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -12484,32 +12484,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>252582</t>
+          <t>291326</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>229978</t>
+          <t>264869</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>276493</t>
+          <t>316683</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>27,37%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>24,89%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>29,05%</t>
+          <t>29,75%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -12519,32 +12519,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>511172</t>
+          <t>581129</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>325366</t>
+          <t>540504</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>589328</t>
+          <t>625225</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>27,56%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>25,64%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>27,52%</t>
+          <t>29,66%</t>
         </is>
       </c>
     </row>
@@ -12562,32 +12562,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>66510</t>
+          <t>77002</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>33538</t>
+          <t>61869</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>93354</t>
+          <t>98745</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -12597,32 +12597,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>79793</t>
+          <t>87887</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>68925</t>
+          <t>73651</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>95058</t>
+          <t>102430</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -12632,32 +12632,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>146303</t>
+          <t>164889</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>95094</t>
+          <t>144053</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>175290</t>
+          <t>189643</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
+          <t>7,82%</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
           <t>6,83%</t>
         </is>
       </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>4,44%</t>
-        </is>
-      </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,99%</t>
         </is>
       </c>
     </row>
@@ -12675,32 +12675,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>28480</t>
+          <t>34436</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13100</t>
+          <t>24659</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>44298</t>
+          <t>49447</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12710,32 +12710,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>34536</t>
+          <t>40287</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>25537</t>
+          <t>30592</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>44086</t>
+          <t>50712</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12745,32 +12745,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>63016</t>
+          <t>74723</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>41992</t>
+          <t>61243</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>80204</t>
+          <t>92991</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>4,41%</t>
         </is>
       </c>
     </row>
@@ -12788,32 +12788,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>18702</t>
+          <t>11827</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6796</t>
+          <t>5882</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>54723</t>
+          <t>20068</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12823,32 +12823,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>14606</t>
+          <t>18254</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>9242</t>
+          <t>11975</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>27459</t>
+          <t>31374</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12858,32 +12858,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>33307</t>
+          <t>30082</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>18665</t>
+          <t>21832</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>67937</t>
+          <t>45619</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>2,16%</t>
         </is>
       </c>
     </row>
@@ -12901,17 +12901,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1189691</t>
+          <t>1043973</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1189691</t>
+          <t>1043973</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1189691</t>
+          <t>1043973</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -12936,17 +12936,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>951784</t>
+          <t>1064355</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>951784</t>
+          <t>1064355</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>951784</t>
+          <t>1064355</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12971,17 +12971,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2141475</t>
+          <t>2108328</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2141475</t>
+          <t>2108328</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2141475</t>
+          <t>2108328</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -13018,32 +13018,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>399876</t>
+          <t>449337</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>369737</t>
+          <t>413963</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>431048</t>
+          <t>479394</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>56,97%</t>
+          <t>56,23%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>52,68%</t>
+          <t>51,8%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>61,41%</t>
+          <t>59,99%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -13053,32 +13053,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>427102</t>
+          <t>461368</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>205623</t>
+          <t>432665</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>564053</t>
+          <t>486231</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>45,97%</t>
+          <t>57,16%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>53,6%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>60,71%</t>
+          <t>60,24%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -13088,32 +13088,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>826977</t>
+          <t>910705</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>539633</t>
+          <t>868964</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>965416</t>
+          <t>955362</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>50,71%</t>
+          <t>56,7%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>33,09%</t>
+          <t>54,1%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>59,19%</t>
+          <t>59,48%</t>
         </is>
       </c>
     </row>
@@ -13131,32 +13131,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>215708</t>
+          <t>246838</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>186249</t>
+          <t>217364</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>244185</t>
+          <t>277689</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>30,73%</t>
+          <t>30,89%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>27,2%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>34,79%</t>
+          <t>34,75%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -13166,32 +13166,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>201863</t>
+          <t>237442</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>98868</t>
+          <t>213619</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>270065</t>
+          <t>259875</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>29,42%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>26,46%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>32,19%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -13201,32 +13201,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>417570</t>
+          <t>484280</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>250226</t>
+          <t>439711</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>495753</t>
+          <t>521345</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>30,15%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>27,37%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>30,4%</t>
+          <t>32,46%</t>
         </is>
       </c>
     </row>
@@ -13244,32 +13244,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>73094</t>
+          <t>79786</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>54679</t>
+          <t>62604</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>94916</t>
+          <t>104216</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -13279,32 +13279,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>279846</t>
+          <t>85050</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>87577</t>
+          <t>70090</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>623128</t>
+          <t>106757</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>67,07%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -13314,32 +13314,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>352940</t>
+          <t>164836</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>157248</t>
+          <t>138549</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>821230</t>
+          <t>192433</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>50,35%</t>
+          <t>11,98%</t>
         </is>
       </c>
     </row>
@@ -13357,32 +13357,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>11516</t>
+          <t>21145</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6811</t>
+          <t>12330</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>18792</t>
+          <t>40583</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -13392,32 +13392,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>14416</t>
+          <t>16079</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7008</t>
+          <t>10234</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>23983</t>
+          <t>24412</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -13427,32 +13427,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>25932</t>
+          <t>37223</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>15827</t>
+          <t>26609</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>35684</t>
+          <t>54999</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>3,42%</t>
         </is>
       </c>
     </row>
@@ -13470,7 +13470,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>1672</t>
+          <t>1979</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -13480,12 +13480,12 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6294</t>
+          <t>7406</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -13495,42 +13495,42 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
+          <t>0,93%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>7274</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>3402</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>13017</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
           <t>0,9%</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>5862</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>11370</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>0,63%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -13540,32 +13540,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>7534</t>
+          <t>9253</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3899</t>
+          <t>4835</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>13509</t>
+          <t>15702</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,98%</t>
         </is>
       </c>
     </row>
@@ -13583,17 +13583,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>701865</t>
+          <t>799084</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>701865</t>
+          <t>799084</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>701865</t>
+          <t>799084</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -13618,17 +13618,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>929089</t>
+          <t>807212</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>929089</t>
+          <t>807212</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>929089</t>
+          <t>807212</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -13653,17 +13653,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1630954</t>
+          <t>1606296</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1630954</t>
+          <t>1606296</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1630954</t>
+          <t>1606296</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -13700,32 +13700,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>614349</t>
+          <t>651017</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>585151</t>
+          <t>619162</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>642470</t>
+          <t>682786</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>66,61%</t>
+          <t>66,04%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>63,45%</t>
+          <t>62,81%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>69,66%</t>
+          <t>69,26%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13735,32 +13735,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>741956</t>
+          <t>728282</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>704640</t>
+          <t>698498</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>805370</t>
+          <t>754896</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>68,3%</t>
+          <t>65,59%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>64,86%</t>
+          <t>62,91%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>74,13%</t>
+          <t>67,99%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13770,32 +13770,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1356306</t>
+          <t>1379298</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1310689</t>
+          <t>1334087</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1430191</t>
+          <t>1415142</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>67,52%</t>
+          <t>65,8%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>65,25%</t>
+          <t>63,65%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>71,2%</t>
+          <t>67,51%</t>
         </is>
       </c>
     </row>
@@ -13813,32 +13813,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>200936</t>
+          <t>214891</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>174887</t>
+          <t>190432</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>226699</t>
+          <t>244030</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>21,8%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>24,76%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -13848,32 +13848,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>230281</t>
+          <t>249503</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>186262</t>
+          <t>227285</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>261498</t>
+          <t>274698</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>22,47%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>24,74%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -13883,32 +13883,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>431218</t>
+          <t>464394</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>379986</t>
+          <t>433104</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>471485</t>
+          <t>502400</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>20,66%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>23,97%</t>
         </is>
       </c>
     </row>
@@ -13926,32 +13926,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>74568</t>
+          <t>82896</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>58783</t>
+          <t>67006</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>91653</t>
+          <t>101254</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13961,32 +13961,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>66861</t>
+          <t>77043</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>52674</t>
+          <t>63520</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>82530</t>
+          <t>93057</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13996,32 +13996,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>141429</t>
+          <t>159939</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>116924</t>
+          <t>138375</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>163439</t>
+          <t>184875</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,82%</t>
         </is>
       </c>
     </row>
@@ -14039,32 +14039,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>22312</t>
+          <t>23759</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>15174</t>
+          <t>16567</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>31945</t>
+          <t>34348</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -14074,32 +14074,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>31950</t>
+          <t>37259</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>22859</t>
+          <t>28977</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>42291</t>
+          <t>47482</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -14109,32 +14109,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>54263</t>
+          <t>61018</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>43303</t>
+          <t>49009</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>67869</t>
+          <t>75792</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,62%</t>
         </is>
       </c>
     </row>
@@ -14152,67 +14152,67 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>10122</t>
+          <t>13209</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>5953</t>
+          <t>7612</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>17928</t>
+          <t>23337</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
+          <t>1,34%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>0,77%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>2,37%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>18258</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>12211</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>25834</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>1,64%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
           <t>1,1%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>0,65%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>1,94%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>15322</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>10276</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>22471</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>1,41%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>0,95%</t>
-        </is>
-      </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -14222,32 +14222,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>25444</t>
+          <t>31467</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>17925</t>
+          <t>23082</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>34425</t>
+          <t>42276</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>2,02%</t>
         </is>
       </c>
     </row>
@@ -14265,17 +14265,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>922288</t>
+          <t>985771</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>922288</t>
+          <t>985771</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>922288</t>
+          <t>985771</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -14300,17 +14300,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1086370</t>
+          <t>1110345</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1086370</t>
+          <t>1110345</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1086370</t>
+          <t>1110345</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -14335,17 +14335,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>2008659</t>
+          <t>2096116</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>2008659</t>
+          <t>2096116</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>2008659</t>
+          <t>2096116</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -14382,32 +14382,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>2237319</t>
+          <t>2162426</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2121861</t>
+          <t>2097031</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2494307</t>
+          <t>2221036</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>64,92%</t>
+          <t>61,49%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>61,57%</t>
+          <t>59,63%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>72,38%</t>
+          <t>63,16%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -14417,32 +14417,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>2135643</t>
+          <t>2245676</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1772035</t>
+          <t>2193259</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2288220</t>
+          <t>2295699</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>58,73%</t>
+          <t>60,56%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>48,73%</t>
+          <t>59,15%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>62,93%</t>
+          <t>61,91%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -14452,32 +14452,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>4372962</t>
+          <t>4408101</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3992649</t>
+          <t>4317838</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4627939</t>
+          <t>4487673</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>61,74%</t>
+          <t>61,02%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>56,37%</t>
+          <t>59,77%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>65,34%</t>
+          <t>62,12%</t>
         </is>
       </c>
     </row>
@@ -14495,32 +14495,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>824106</t>
+          <t>916241</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>654194</t>
+          <t>861263</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>910993</t>
+          <t>973690</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>26,06%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>27,69%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -14530,32 +14530,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>863206</t>
+          <t>972049</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>709670</t>
+          <t>926886</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>940798</t>
+          <t>1018085</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>26,21%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>25,87%</t>
+          <t>27,46%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -14565,32 +14565,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>1687312</t>
+          <t>1888290</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1453328</t>
+          <t>1815775</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1805346</t>
+          <t>1963843</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>25,13%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>27,18%</t>
         </is>
       </c>
     </row>
@@ -14608,32 +14608,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>263493</t>
+          <t>297385</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>209242</t>
+          <t>263815</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>309649</t>
+          <t>334609</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14643,32 +14643,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>489638</t>
+          <t>318637</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>291394</t>
+          <t>291481</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1033274</t>
+          <t>350972</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>28,42%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14678,32 +14678,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>753131</t>
+          <t>616022</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>544763</t>
+          <t>576201</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1498854</t>
+          <t>666790</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>9,23%</t>
         </is>
       </c>
     </row>
@@ -14721,32 +14721,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>79022</t>
+          <t>98738</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>58723</t>
+          <t>79942</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>98406</t>
+          <t>119520</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -14756,32 +14756,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>104447</t>
+          <t>118966</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>83052</t>
+          <t>103919</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>122651</t>
+          <t>137254</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -14791,32 +14791,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>183469</t>
+          <t>217704</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>154834</t>
+          <t>191255</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>209576</t>
+          <t>247010</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,42%</t>
         </is>
       </c>
     </row>
@@ -14834,32 +14834,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>42406</t>
+          <t>41685</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>28694</t>
+          <t>29792</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>78293</t>
+          <t>57358</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -14869,32 +14869,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>43299</t>
+          <t>52752</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>32174</t>
+          <t>40005</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>58428</t>
+          <t>66879</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -14904,32 +14904,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>85705</t>
+          <t>94437</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>67751</t>
+          <t>78140</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>122743</t>
+          <t>117344</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,62%</t>
         </is>
       </c>
     </row>
@@ -14947,17 +14947,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>3446347</t>
+          <t>3516475</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>3446347</t>
+          <t>3516475</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>3446347</t>
+          <t>3516475</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -14982,17 +14982,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>3636233</t>
+          <t>3708079</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>3636233</t>
+          <t>3708079</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>3636233</t>
+          <t>3708079</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -15017,17 +15017,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>7082580</t>
+          <t>7224553</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>7082580</t>
+          <t>7224553</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>7082580</t>
+          <t>7224553</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
